--- a/QB Data Project/excel_ready_data/qb_data_created.xlsx
+++ b/QB Data Project/excel_ready_data/qb_data_created.xlsx
@@ -24,16 +24,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,42 +424,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Passing Yards 2015-2024</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total passing TDs 2015-2024</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total Interceptions 2015-2024</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Games Played 2015-2024</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Completion Pct 2015-2024</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Yards per att 2015-2024</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Passer Rating 2015-2024</t>
         </is>
@@ -1332,12 +1320,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Average Passing Yards</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
@@ -1438,52 +1426,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Passer Rating</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Passing Yards</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Passing TDs</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Interceptions</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Completion Pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Yards Per Att</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Games Played</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Current Team</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
@@ -2584,12 +2572,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>AVG Yards Thrown Downfield</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
@@ -2597,7 +2585,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7.62</v>
+        <v>7.51</v>
       </c>
       <c r="B2" t="n">
         <v>2024</v>
@@ -2605,7 +2593,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8.1</v>
+        <v>7.88</v>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
@@ -2613,7 +2601,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7.81</v>
+        <v>7.7</v>
       </c>
       <c r="B4" t="n">
         <v>2022</v>
@@ -2621,7 +2609,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7.59</v>
+        <v>7.16</v>
       </c>
       <c r="B5" t="n">
         <v>2021</v>
@@ -2629,7 +2617,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8.01</v>
+        <v>7.9</v>
       </c>
       <c r="B6" t="n">
         <v>2020</v>
@@ -2637,7 +2625,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.31</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="B7" t="n">
         <v>2019</v>
@@ -2645,7 +2633,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8.449999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="B8" t="n">
         <v>2018</v>
@@ -2661,7 +2649,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8.82</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="B10" t="n">
         <v>2016</v>
@@ -2669,7 +2657,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8.5</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="B11" t="n">
         <v>2015</v>
@@ -2690,42 +2678,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Yards</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total TDs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total Passing Yards</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Rushing Yards</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Pass TDs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Rush TDs</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Seasons Played from 2015-2024</t>
         </is>
@@ -3586,27 +3574,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Average QB Rushing</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Average QB Yards Per Rush</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>QB Rushing TDs Per Season</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AVG QB Rush Attempts</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
@@ -3797,32 +3785,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TD to INT Ratio</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Passing Toucdowns</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Interceptions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Completion Pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
@@ -4503,42 +4491,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Playoff Passing Yards</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Playoff Passing TDs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total Playoff Interceptions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Playoff Yards</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Playoff TDs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Average Passer Rating</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Playoff Appearances</t>
         </is>
